--- a/data/trans_dic/IP31KM12_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,88; 100,0</t>
+          <t>95,52; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,17; 100,0</t>
+          <t>95,42; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96,9; 100,0</t>
+          <t>96,96; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,78; 99,35</t>
+          <t>94,06; 99,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,8; 99,17</t>
+          <t>95,72; 99,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,08; 99,0</t>
+          <t>95,96; 98,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,07; 99,73</t>
+          <t>97,49; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,5; 100,0</t>
+          <t>97,09; 99,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98,02; 99,81</t>
+          <t>98,05; 99,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>92,49; 97,28</t>
+          <t>98,82; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>98,71; 100,0</t>
+          <t>91,55; 96,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,08; 98,53</t>
+          <t>95,78; 98,35</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>95,96; 98,23</t>
+          <t>98,26; 99,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>98,26; 99,56</t>
+          <t>95,71; 97,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,49; 98,75</t>
+          <t>97,31; 98,67</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46034</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>42299</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90927</t>
+          <t>79412</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44112; 46495</t>
+          <t>35758; 37435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43096; 45285</t>
+          <t>40728; 42681</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88934; 91779</t>
+          <t>77680; 80116</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>253</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>156335</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>177673</t>
+          <t>142868</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334009</t>
+          <t>295916</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>152573; 158260</t>
+          <t>147719; 155557</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172488; 180440</t>
+          <t>139297; 144465</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>327868; 337842</t>
+          <t>290330; 299237</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>230</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>171332</t>
+          <t>199111</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>211432</t>
+          <t>172877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>382765</t>
+          <t>371987</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>168000; 172613</t>
+          <t>195098; 200126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>207176; 212490</t>
+          <t>169582; 174187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>377941; 384839</t>
+          <t>367485; 374091</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>323</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>260984</t>
+          <t>291294</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304002</t>
+          <t>241501</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>564986</t>
+          <t>532795</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>253659; 266816</t>
+          <t>288773; 292221</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>301069; 304999</t>
+          <t>233767; 246827</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>556558; 570737</t>
+          <t>524452; 538530</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>888</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>634685</t>
+          <t>680565</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599545</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1372687</t>
+          <t>1280109</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>626735; 641562</t>
+          <t>674888; 684044</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>731772; 741486</t>
+          <t>591684; 605462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1362794; 1380432</t>
+          <t>1269948; 1287702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM12_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>95,52; 100,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>95,42; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>96,96; 100,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>94,06; 99,05</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>95,72; 99,28</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>95,96; 98,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>97,49; 100,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>97,09; 99,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>98,05; 99,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>98,82; 100,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>91,55; 96,67</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>95,78; 98,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>98,26; 99,6</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>95,71; 97,94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97,31; 98,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9913832324110209</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9910553084695336</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9912085349905012</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>37112</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>42299</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>79412</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.9551914286509655</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9542431187452138</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9695916401137753</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>35758; 37435</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>40728; 42681</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>77680; 80116</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9745684296488295</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9817903726323386</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9780418606890838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>153048</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>142868</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>295916</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9406336705675038</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9572470378197631</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.959577936858838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>147719; 155557</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>139297; 144465</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>290330; 299237</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9905409373847079</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9927644688124955</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9890157698179614</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9949275001610988</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9897212288279711</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9925011504627479</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>199111</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>172877</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>371987</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.974874629680368</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9708594236992141</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9804878043718692</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>195098; 200126</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>169582; 174187</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>367485; 374091</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9972261037704749</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9981149584715063</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9968272503241133</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.945813141924191</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9730383594931089</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>291294</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>241501</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>532795</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9881999617492155</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9155246749263497</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9578025105148875</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>288773; 292221</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>233767; 246827</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>524452; 538530</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9666706853560751</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9835117103509579</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1819</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9908875051379264</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9698112443779168</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9809034490817417</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>680565</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>599545</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1280109</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.9826209889953467</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9570958060483092</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9731174152426754</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>674888; 684044</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>591684; 605462</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1269948; 1287702</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9959517066210481</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.979381608515451</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9867210053714085</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>37112</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>42299</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>79412</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>35758</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>40728</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>77680</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>37435</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42681</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>80116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>253</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>153048</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>142868</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>295916</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>147719</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>139297</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>290330</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>155557</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>144465</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>299237</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>199111</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>172877</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>371987</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>195098</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>169582</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>367485</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>200126</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>174187</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>374091</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>339</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>291294</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>241501</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>532795</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>288773</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>233767</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>524452</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>292221</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>246827</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>538530</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>931</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>888</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>680565</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>599545</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1280109</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>674888</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>591684</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1269948</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>684044</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>605462</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1287702</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>